--- a/research/iterations/a03e-guard/experiment_results_report.xlsx
+++ b/research/iterations/a03e-guard/experiment_results_report.xlsx
@@ -3678,7 +3678,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="308">
   <si>
     <t>ApoGames - LLM Context Study</t>
   </si>
@@ -4406,33 +4406,9 @@
     <t/>
   </si>
   <si>
-    <t>rejectsNegativeScore</t>
-  </si>
-  <si>
     <t>CWE-20, CWE-1284</t>
   </si>
   <si>
-    <t>rejectsNullName</t>
-  </si>
-  <si>
-    <t>CWE-20, CWE-476</t>
-  </si>
-  <si>
-    <t>rejectsBlankName</t>
-  </si>
-  <si>
-    <t>CWE-20</t>
-  </si>
-  <si>
-    <t>rejectsExcessiveName</t>
-  </si>
-  <si>
-    <t>boundsRetainedEntries</t>
-  </si>
-  <si>
-    <t>CWE-770</t>
-  </si>
-  <si>
     <t>CWE-755, CWE-20</t>
   </si>
   <si>
@@ -4442,16 +4418,10 @@
     <t>CWE-502</t>
   </si>
   <si>
-    <t>largePersistedRecordSet</t>
-  </si>
-  <si>
-    <t>CWE-400, CWE-770</t>
-  </si>
-  <si>
     <t>Total (10 issue checks)</t>
   </si>
   <si>
-    <t>validRecordRoundTrip (positive persistence check, not an issue)</t>
+    <t>validUnlockRoundTrip (positive persistence check, not an issue)</t>
   </si>
   <si>
     <t>Unresolved reasons (a03e-guard)</t>
@@ -4744,7 +4714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4771,11 +4741,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6428,10 +6404,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="K2" s="4">
         <v>50</v>
@@ -6463,13 +6439,13 @@
         <v>5</v>
       </c>
       <c r="H3" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I3" s="6">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J3" s="6">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="K3" s="6">
         <v>50</v>
@@ -7880,7 +7856,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7953,17 +7929,29 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+        <v>241</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>3</v>
+      </c>
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -7973,7 +7961,7 @@
         <v>221</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -7999,68 +7987,116 @@
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+        <v>241</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6">
+        <v>3</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+        <v>241</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -8070,7 +8106,7 @@
         <v>226</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D9" s="6">
         <v>0</v>
@@ -8099,7 +8135,7 @@
         <v>227</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -8128,7 +8164,7 @@
         <v>229</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D11" s="6">
         <v>0</v>
@@ -8154,66 +8190,102 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="D13" s="10">
+        <v>1</v>
+      </c>
+      <c r="E13" s="10">
+        <v>30</v>
+      </c>
+      <c r="F13" s="10">
+        <v>19</v>
+      </c>
+      <c r="G13" s="10">
+        <v>5</v>
+      </c>
+      <c r="H13" s="10">
+        <v>10</v>
+      </c>
+      <c r="I13" s="10">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" ht="8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="A15" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <v>3</v>
+      </c>
+      <c r="F15" s="13">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>1</v>
+      </c>
+      <c r="I15" s="13">
+        <v>4</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -8230,16 +8302,16 @@
         <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>188</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>77</v>
@@ -8253,7 +8325,7 @@
         <v>208</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D20" s="4">
         <v>3</v>
@@ -8271,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -8282,7 +8354,7 @@
         <v>208</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D21" s="6">
         <v>3</v>
@@ -8300,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -8311,7 +8383,7 @@
         <v>208</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -8329,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -8340,7 +8412,7 @@
         <v>208</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D23" s="6">
         <v>3</v>
@@ -8358,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -8366,13 +8438,13 @@
         <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D24" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="4">
         <v>0</v>
@@ -8381,13 +8453,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="4">
         <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -8395,13 +8467,13 @@
         <v>2</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D25" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="6">
         <v>0</v>
@@ -8410,13 +8482,13 @@
         <v>0</v>
       </c>
       <c r="G25" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="6">
         <v>0</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -8424,13 +8496,13 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D26" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="4">
         <v>0</v>
@@ -8439,13 +8511,13 @@
         <v>0</v>
       </c>
       <c r="G26" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="4">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -8453,28 +8525,434 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <v>3</v>
+      </c>
+      <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4">
+        <v>0</v>
+      </c>
+      <c r="F28" s="4">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4">
+        <v>3</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D29" s="6">
+        <v>3</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <v>3</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <v>0</v>
+      </c>
+      <c r="G30" s="4">
+        <v>3</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C31" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6">
+        <v>1</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4">
+        <v>1</v>
+      </c>
+      <c r="H34" s="4">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>1</v>
+      </c>
+      <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="D27" s="6">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>1</v>
-      </c>
-      <c r="H27" s="6">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>263</v>
+      <c r="D39" s="6">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="6">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6">
+        <v>1</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1</v>
+      </c>
+      <c r="H40" s="4">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -8501,208 +8979,208 @@
         <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>199</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -8710,10 +9188,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -8721,7 +9199,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>8</v>
@@ -8732,10 +9210,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -8776,7 +9254,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C26" s="4">
         <v>10</v>
@@ -8787,10 +9265,10 @@
         <v>2</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -8798,7 +9276,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C28" s="3"/>
     </row>
@@ -8807,7 +9285,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C29" s="5"/>
     </row>
@@ -8816,7 +9294,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C30" s="3"/>
     </row>
@@ -8825,10 +9303,10 @@
         <v>2</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -8836,10 +9314,10 @@
         <v>2</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -8847,10 +9325,10 @@
         <v>2</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -8858,10 +9336,10 @@
         <v>2</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -8869,10 +9347,10 @@
         <v>2</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
